--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -578,8 +578,10 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>103</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -653,8 +655,10 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>103</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>

--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">

--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job History" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -676,8 +676,83 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>eef17e6ffbd5fcc3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://career.luxoft.com/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Regular Software Engineer Java Krakow Poland</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://career.luxoft.com/jobs/regular-software-engineer-26719</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>software engineer java</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>103</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O3"/>
+  <autoFilter ref="A1:O4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -732,12 +732,14 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>103</v>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">

--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job History" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -753,8 +753,1658 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>958584b0e00fb2a6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-euse-java-aix-en-provence-in-aix-en-provence-france-jid-5854</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>60</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>e0c2e763389249fb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-transport-and-mobility-m-w-d-in-bundesweit-germany-jid-7385</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>60</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>f59eedfdb81604eb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-sales-and-growth-im-produktgeschaeft-m-w-d-in-hamburg-germany-jid-9258</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>60</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6639b28e3e83df1b</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-sap-data-and-analytics-m-w-d-in-bundesweit-germany-jid-2750</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>60</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>db41fec42eff7fc7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-project-management-office-im-public-sector-m-w-d-in-bundesweit-germany-jid-2906</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>60</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7e7876fb53aec018</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-mit-schwerpunkt-fachliche-unterstuetzung-in-leitstellenloesungen-m-w-d-in-berlin-frankfurt-germany-jid-9269</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>60</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>c7d16ed243960564</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-java-entwicklung-m-w-d-in-leipzig-germany-jid-7640</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>60</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>06c47b6859dcf9d9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-integration-and-service-schwerpunkt-it-m-w-d-in-berlin-frankfurt-germany-jid-9270</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>60</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3add5db664f895b3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-frontend-and-backend-entwicklung-m-w-d-in-hamburg-germany-jid-2655</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>60</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>75512c01a06f9149</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-entwickler-prozessautomatisierung-m-w-d-in-bundesweit-germany-jid-9511</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>60</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>e6f90d90e6d9ac49</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-data-engineer-analyst-m-w-d-in-hamburg-germany-jid-3431</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>60</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>bcf6618b2c949330</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-devsecops-im-solution-center-m-w-d-in-berlin-frankfurt-germany-jid-9280</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>60</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00340054a5ab077b</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-cybersecurity-m-w-d-in-bundesweit-germany-jid-3153</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>60</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>521187917c773da4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-cyber-security-vulnerability-management-and-edr-m-w-d-in-muenchen-germany-jid-9255</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>60</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>39d7af8a3712173d</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-accounting-and-finanzprozesse-m-w-d-purchase-to-pay-p2p-in-bundesweit-germany-jid-9250</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>60</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>b35b4abb2ec1b6cf</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/werkstudent-m-w-d-hr-digitalisierung-and-prozessautomatisierung-am-standort-hamburg-in-hamburg-germany-jid-9329</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>60</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cc643671602a4ad6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/vil-du-v-re-med-a-forme-lede-fremtidens-utviklermilj-pa-hamar-in-hamar-norway-jid-9560</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>60</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>e89acee1e60e4e15</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/business-owner-erp-in-stockholm-sweden-jid-9545</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>60</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>e2c7cfa23e04ecc5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/ingeniero-cloud-in-madrid-spain-jid-9559</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>60</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>f264b25e9b13643e</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/manager-adjoint-e-strategie-cybersecurite-toulouse-in-toulouse-france-jid-7122</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>60</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2718ac706b7b8fca</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/#/</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>60</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>71596b406dea22d9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>View all</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/jobs</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>java, git</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>associate</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>60</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O4"/>
+  <autoFilter ref="A1:O26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -809,12 +809,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>60</v>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -884,12 +886,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>60</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -959,12 +963,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>60</v>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1034,12 +1040,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>60</v>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1109,12 +1117,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>60</v>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1184,12 +1194,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>60</v>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1259,12 +1271,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>60</v>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1334,12 +1348,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>60</v>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1409,12 +1425,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>60</v>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1484,12 +1502,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>60</v>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1559,12 +1579,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>60</v>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1634,12 +1656,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>60</v>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1709,12 +1733,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L17" t="n">
-        <v>60</v>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1784,12 +1810,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L18" t="n">
-        <v>60</v>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1859,12 +1887,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L19" t="n">
-        <v>60</v>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1934,12 +1964,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L20" t="n">
-        <v>60</v>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2009,12 +2041,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>60</v>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2084,12 +2118,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>60</v>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2159,12 +2195,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>60</v>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2234,12 +2272,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>60</v>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2309,12 +2349,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>60</v>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2384,12 +2426,14 @@
           <t>associate</t>
         </is>
       </c>
-      <c r="L26" t="n">
-        <v>60</v>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
